--- a/main/ig/StructureDefinition-ExerciceProfessionnel.xlsx
+++ b/main/ig/StructureDefinition-ExerciceProfessionnel.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="929" uniqueCount="150">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1084" uniqueCount="165">
   <si>
     <t>Property</t>
   </si>
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-12-03T08:56:12+00:00</t>
+    <t>2026-03-06T09:16:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -463,14 +463,64 @@
     <t>Date à laquelle le niveau de formation n’est plus actif (non visible hormis dans les données historisées). Cette date est renseignée par l’ordre à la clôture de l’exercice professionnel.</t>
   </si>
   <si>
-    <t>ExerciceProfessionnel.professionnel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reference(https://interop.esante.gouv.fr/ig/mos/StructureDefinition/Professionnel)
+    <t>ExerciceProfessionnel.SituationExercice</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/mos/StructureDefinition/SituationExercice
 </t>
   </si>
   <si>
-    <t>Lien vers la classe Professionnel.</t>
+    <t>Lien vers la classe SituationExercice</t>
+  </si>
+  <si>
+    <t>ExerciceProfessionnel.Certificat</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/mos/StructureDefinition/Certificat
+</t>
+  </si>
+  <si>
+    <t>Lien vers la classe Certificat</t>
+  </si>
+  <si>
+    <t>ExerciceProfessionnel.SavoirFaire</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/mos/StructureDefinition/SavoirFaire
+</t>
+  </si>
+  <si>
+    <t>Lien vers la classe SavoirFaire</t>
+  </si>
+  <si>
+    <t>ExerciceProfessionnel.CarteProfessionnel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/mos/StructureDefinition/CarteProfessionnel
+</t>
+  </si>
+  <si>
+    <t>Lien vers la classe CarteProfessionnel</t>
+  </si>
+  <si>
+    <t>ExerciceProfessionnel.Professionnel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/mos/StructureDefinition/Professionnel
+</t>
+  </si>
+  <si>
+    <t>Lien vers la classe Professionnel</t>
+  </si>
+  <si>
+    <t>ExerciceProfessionnel.SituationOperationnelle</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/mos/StructureDefinition/SituationOperationnelle
+</t>
+  </si>
+  <si>
+    <t>Lien vers la classe SituationOperationnelle</t>
   </si>
 </sst>
 </file>
@@ -772,7 +822,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AJ29"/>
+  <dimension ref="A1:AJ34"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="57.42578125" customWidth="true" bestFit="true"/>
@@ -785,7 +835,7 @@
     <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="65.640625" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="64.53125" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -3611,10 +3661,10 @@
       </c>
       <c r="E29" s="2"/>
       <c r="F29" t="s" s="2">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="G29" t="s" s="2">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="H29" t="s" s="2">
         <v>71</v>
@@ -3686,15 +3736,515 @@
         <v>147</v>
       </c>
       <c r="AG29" t="s" s="2">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="AH29" t="s" s="2">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="AI29" t="s" s="2">
         <v>71</v>
       </c>
       <c r="AJ29" t="s" s="2">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="s" s="2">
+        <v>150</v>
+      </c>
+      <c r="B30" t="s" s="2">
+        <v>150</v>
+      </c>
+      <c r="C30" s="2"/>
+      <c r="D30" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="E30" s="2"/>
+      <c r="F30" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="G30" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="H30" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="I30" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="J30" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="K30" t="s" s="2">
+        <v>151</v>
+      </c>
+      <c r="L30" t="s" s="2">
+        <v>152</v>
+      </c>
+      <c r="M30" t="s" s="2">
+        <v>152</v>
+      </c>
+      <c r="N30" s="2"/>
+      <c r="O30" s="2"/>
+      <c r="P30" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="Q30" s="2"/>
+      <c r="R30" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="S30" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="T30" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="U30" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="V30" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="W30" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="X30" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="Y30" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="Z30" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="AA30" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="AB30" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="AC30" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="AD30" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="AE30" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="AF30" t="s" s="2">
+        <v>150</v>
+      </c>
+      <c r="AG30" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AH30" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AI30" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="AJ30" t="s" s="2">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="s" s="2">
+        <v>153</v>
+      </c>
+      <c r="B31" t="s" s="2">
+        <v>153</v>
+      </c>
+      <c r="C31" s="2"/>
+      <c r="D31" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="E31" s="2"/>
+      <c r="F31" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="G31" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="H31" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="I31" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="J31" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="K31" t="s" s="2">
+        <v>154</v>
+      </c>
+      <c r="L31" t="s" s="2">
+        <v>155</v>
+      </c>
+      <c r="M31" t="s" s="2">
+        <v>155</v>
+      </c>
+      <c r="N31" s="2"/>
+      <c r="O31" s="2"/>
+      <c r="P31" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="Q31" s="2"/>
+      <c r="R31" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="S31" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="T31" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="U31" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="V31" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="W31" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="X31" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="Y31" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="Z31" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="AA31" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="AB31" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="AC31" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="AD31" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="AE31" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="AF31" t="s" s="2">
+        <v>153</v>
+      </c>
+      <c r="AG31" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AH31" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AI31" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="AJ31" t="s" s="2">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="s" s="2">
+        <v>156</v>
+      </c>
+      <c r="B32" t="s" s="2">
+        <v>156</v>
+      </c>
+      <c r="C32" s="2"/>
+      <c r="D32" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="E32" s="2"/>
+      <c r="F32" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="G32" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="H32" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="I32" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="J32" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="K32" t="s" s="2">
+        <v>157</v>
+      </c>
+      <c r="L32" t="s" s="2">
+        <v>158</v>
+      </c>
+      <c r="M32" t="s" s="2">
+        <v>158</v>
+      </c>
+      <c r="N32" s="2"/>
+      <c r="O32" s="2"/>
+      <c r="P32" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="Q32" s="2"/>
+      <c r="R32" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="S32" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="T32" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="U32" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="V32" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="W32" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="X32" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="Y32" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="Z32" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="AA32" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="AB32" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="AC32" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="AD32" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="AE32" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="AF32" t="s" s="2">
+        <v>156</v>
+      </c>
+      <c r="AG32" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AH32" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AI32" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="AJ32" t="s" s="2">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="s" s="2">
+        <v>159</v>
+      </c>
+      <c r="B33" t="s" s="2">
+        <v>159</v>
+      </c>
+      <c r="C33" s="2"/>
+      <c r="D33" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="E33" s="2"/>
+      <c r="F33" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="G33" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="H33" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="I33" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="J33" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="K33" t="s" s="2">
+        <v>160</v>
+      </c>
+      <c r="L33" t="s" s="2">
+        <v>161</v>
+      </c>
+      <c r="M33" t="s" s="2">
+        <v>161</v>
+      </c>
+      <c r="N33" s="2"/>
+      <c r="O33" s="2"/>
+      <c r="P33" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="Q33" s="2"/>
+      <c r="R33" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="S33" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="T33" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="U33" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="V33" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="W33" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="X33" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="Y33" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="Z33" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="AA33" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="AB33" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="AC33" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="AD33" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="AE33" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="AF33" t="s" s="2">
+        <v>159</v>
+      </c>
+      <c r="AG33" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH33" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AI33" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="AJ33" t="s" s="2">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="s" s="2">
+        <v>162</v>
+      </c>
+      <c r="B34" t="s" s="2">
+        <v>162</v>
+      </c>
+      <c r="C34" s="2"/>
+      <c r="D34" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="E34" s="2"/>
+      <c r="F34" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="G34" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="H34" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="I34" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="J34" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="K34" t="s" s="2">
+        <v>163</v>
+      </c>
+      <c r="L34" t="s" s="2">
+        <v>164</v>
+      </c>
+      <c r="M34" t="s" s="2">
+        <v>164</v>
+      </c>
+      <c r="N34" s="2"/>
+      <c r="O34" s="2"/>
+      <c r="P34" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="Q34" s="2"/>
+      <c r="R34" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="S34" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="T34" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="U34" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="V34" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="W34" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="X34" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="Y34" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="Z34" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="AA34" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="AB34" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="AC34" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="AD34" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="AE34" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="AF34" t="s" s="2">
+        <v>162</v>
+      </c>
+      <c r="AG34" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AH34" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AI34" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="AJ34" t="s" s="2">
         <v>71</v>
       </c>
     </row>

--- a/main/ig/StructureDefinition-ExerciceProfessionnel.xlsx
+++ b/main/ig/StructureDefinition-ExerciceProfessionnel.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-06T09:16:42+00:00</t>
+    <t>2026-04-20T07:14:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-ExerciceProfessionnel.xlsx
+++ b/main/ig/StructureDefinition-ExerciceProfessionnel.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.1.0</t>
+    <t>0.1.0-ballot</t>
   </si>
   <si>
     <t>Name</t>
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-20T07:14:21+00:00</t>
+    <t>2026-04-20T13:39:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-ExerciceProfessionnel.xlsx
+++ b/main/ig/StructureDefinition-ExerciceProfessionnel.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-20T13:39:43+00:00</t>
+    <t>2026-04-20T13:49:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-ExerciceProfessionnel.xlsx
+++ b/main/ig/StructureDefinition-ExerciceProfessionnel.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-20T13:49:18+00:00</t>
+    <t>2026-04-20T13:52:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-ExerciceProfessionnel.xlsx
+++ b/main/ig/StructureDefinition-ExerciceProfessionnel.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-20T13:52:11+00:00</t>
+    <t>2026-04-20T14:01:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-ExerciceProfessionnel.xlsx
+++ b/main/ig/StructureDefinition-ExerciceProfessionnel.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-20T14:01:02+00:00</t>
+    <t>2026-04-20T14:11:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-ExerciceProfessionnel.xlsx
+++ b/main/ig/StructureDefinition-ExerciceProfessionnel.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-20T14:11:31+00:00</t>
+    <t>2026-04-20T14:36:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -72,7 +72,7 @@
     <t>Jurisdiction</t>
   </si>
   <si>
-    <t>FRANCE</t>
+    <t>France (la)</t>
   </si>
   <si>
     <t>Description</t>

--- a/main/ig/StructureDefinition-ExerciceProfessionnel.xlsx
+++ b/main/ig/StructureDefinition-ExerciceProfessionnel.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-20T14:36:06+00:00</t>
+    <t>2026-04-20T14:56:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
